--- a/consent_forms/033_power_of_attorney_consent_form--consent_forms.xlsx
+++ b/consent_forms/033_power_of_attorney_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'self'}</t>
+          <t>self</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Self'}</t>
+          <t>Self</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'family_member'}</t>
+          <t>family_member</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Family Member'}</t>
+          <t>Family Member</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'friend'}</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Friend'}</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'parent/child'}</t>
+          <t>parent/child</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Parent/Child'}</t>
+          <t>Parent/Child</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'sibling'}</t>
+          <t>sibling</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Sibling'}</t>
+          <t>Sibling</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'family_friend'}</t>
+          <t>family_friend</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Family Friend'}</t>
+          <t>Family Friend</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'financial'}</t>
+          <t>financial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Financial'}</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'real_estate'}</t>
+          <t>real_estate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Real Estate'}</t>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'health_care'}</t>
+          <t>health_care</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Health Care'}</t>
+          <t>Health Care</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
